--- a/data/contributors.xlsx
+++ b/data/contributors.xlsx
@@ -184,7 +184,7 @@
     <t xml:space="preserve">prohibitives</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejective p</t>
+    <t xml:space="preserve">Ejective *p*</t>
   </si>
   <si>
     <t xml:space="preserve">George Moroz, Vasiliy Zerzele</t>
@@ -211,7 +211,7 @@
     <t xml:space="preserve">Garik</t>
   </si>
   <si>
-    <t xml:space="preserve">Ejective s</t>
+    <t xml:space="preserve">Ejective *s*</t>
   </si>
   <si>
     <t xml:space="preserve">ejective_s</t>
@@ -751,7 +751,7 @@
     <t xml:space="preserve">maize</t>
   </si>
   <si>
-    <t xml:space="preserve">Meaning of words hajwan and janawar</t>
+    <t xml:space="preserve">Meaning of the words *hajwan* and *janawar*</t>
   </si>
   <si>
     <t xml:space="preserve">Dasha Tsikh</t>
@@ -1083,7 +1083,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="86.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14.25"/>

--- a/data/contributors.xlsx
+++ b/data/contributors.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="246">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -754,7 +754,7 @@
     <t xml:space="preserve">Meaning of the words *hajwan* and *janawar*</t>
   </si>
   <si>
-    <t xml:space="preserve">Dasha Tsikh</t>
+    <t xml:space="preserve">Daria Tsikh</t>
   </si>
   <si>
     <t xml:space="preserve">hajwan_and_janawar</t>
@@ -852,7 +852,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -886,6 +886,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4592,7 +4596,9 @@
         <v>242</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
+      <c r="M74" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="N74" s="7" t="s">
         <v>29</v>
       </c>
@@ -4636,7 +4642,9 @@
         <v>245</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" s="9" t="s">
+        <v>61</v>
+      </c>
       <c r="N75" s="7" t="s">
         <v>29</v>
       </c>
